--- a/changes/optics.xlsx
+++ b/changes/optics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whyth\Documents\GitHub\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A13C4A-9B12-41EF-9160-BCDC012B9490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507D9A2D-49AB-43DE-873B-C3800A4D977C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="m4-barrels" sheetId="1" r:id="rId1"/>
@@ -1569,9 +1569,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1936,64 +1935,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" t="s">
         <v>3</v>
       </c>
       <c r="P2" t="s">
@@ -2007,30 +1993,22 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.02</v>
+      </c>
+      <c r="M3">
         <v>200</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3">
         <f>C3-D3*20-E3*0.8-F3*0.6-H3*5+I3*10+J3/300</f>
         <v>-0.4</v>
       </c>
@@ -2040,30 +2018,22 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0.02</v>
+      </c>
+      <c r="M4">
         <v>300</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4">
         <f t="shared" ref="N4:N5" si="0">C4-D4*20-E4*0.8-F4*0.6-H4*5+I4*10+J4/300</f>
         <v>-0.4</v>
       </c>
@@ -2073,30 +2043,22 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>-1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>0.05</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1">
+      <c r="M5">
         <v>350</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
@@ -2106,30 +2068,22 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>-2</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>0.04</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1">
+      <c r="M6">
         <v>1100</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6">
         <f t="shared" ref="N6:N32" si="2">C6-D6*20-E6*0.8-F6*0.6-H6*5+I6*10+J6/300</f>
         <v>-2.8</v>
       </c>
@@ -2145,30 +2099,22 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>-2</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>0.04</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1">
+      <c r="M7">
         <v>1200</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7">
         <f t="shared" si="2"/>
         <v>-2.8</v>
       </c>
@@ -2184,30 +2130,22 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>-2</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8">
         <v>0.04</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1">
+      <c r="M8">
         <v>1000</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8">
         <f t="shared" si="2"/>
         <v>-2.8</v>
       </c>
@@ -2223,30 +2161,22 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>-2</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>0.04</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1">
+      <c r="M9">
         <v>800</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9">
         <f t="shared" si="2"/>
         <v>-2.8</v>
       </c>
@@ -2262,30 +2192,22 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>-2</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>0.04</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1">
+      <c r="M10">
         <v>800</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10">
         <f t="shared" si="2"/>
         <v>-2.8</v>
       </c>
@@ -2298,55 +2220,54 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>321</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <f>C4+C6</f>
         <v>-2</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <f t="shared" ref="D11:M11" si="3">D4+D6</f>
         <v>0.06</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M11">
         <f t="shared" si="3"/>
         <v>1400</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11">
         <f t="shared" si="2"/>
         <v>-3.2</v>
       </c>
@@ -2356,103 +2277,81 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>322</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <f>C5+C6</f>
         <v>-3</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <f t="shared" ref="D12:M12" si="4">D5+D6</f>
         <v>0.09</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12">
         <f t="shared" si="4"/>
         <v>1450</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12">
         <f t="shared" si="2"/>
         <v>-4.8</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1">
+      <c r="N13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0.02</v>
+      </c>
+      <c r="M14">
         <v>200</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14">
         <f t="shared" si="2"/>
         <v>-0.4</v>
       </c>
@@ -2462,30 +2361,22 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <v>-1</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <v>0.05</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1">
+      <c r="M15">
         <v>250</v>
       </c>
-      <c r="N15" s="1">
+      <c r="N15">
         <f t="shared" si="2"/>
         <v>-2</v>
       </c>
@@ -2495,30 +2386,22 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>-1</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1">
+      <c r="M16">
         <v>300</v>
       </c>
-      <c r="N16" s="1">
+      <c r="N16">
         <f t="shared" si="2"/>
         <v>-2.4000000000000004</v>
       </c>
@@ -2543,7 +2426,7 @@
       <c r="M17">
         <v>800</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17">
         <f t="shared" si="2"/>
         <v>-2.8</v>
       </c>
@@ -2553,30 +2436,22 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18">
         <v>-2</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18">
         <v>0.05</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1">
+      <c r="M18">
         <v>1200</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18">
         <f t="shared" si="2"/>
         <v>-3</v>
       </c>
@@ -2589,30 +2464,22 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>279</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>-2</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19">
         <v>0.05</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1">
+      <c r="M19">
         <v>1100</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19">
         <f t="shared" si="2"/>
         <v>-3</v>
       </c>
@@ -2625,128 +2492,113 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>323</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20">
         <f>C18+C14</f>
         <v>-2</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20">
         <f t="shared" ref="D20:M20" si="5">D18+D14</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M20">
         <f t="shared" si="5"/>
         <v>1400</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20">
         <f t="shared" si="2"/>
         <v>-3.4000000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21">
         <f>C18+C15</f>
         <v>-3</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21">
         <f t="shared" ref="D21:M21" si="6">D18+D15</f>
         <v>0.1</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M21">
         <f t="shared" si="6"/>
         <v>1450</v>
       </c>
-      <c r="N21" s="1">
+      <c r="N21">
         <f t="shared" si="2"/>
         <v>-5</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1">
+      <c r="N22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2771,7 +2623,7 @@
       <c r="M23">
         <v>200</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N23">
         <f t="shared" si="2"/>
         <v>-0.4</v>
       </c>
@@ -2796,7 +2648,7 @@
       <c r="M24">
         <v>300</v>
       </c>
-      <c r="N24" s="1">
+      <c r="N24">
         <f t="shared" si="2"/>
         <v>-1.8</v>
       </c>
@@ -2821,7 +2673,7 @@
       <c r="M25">
         <v>900</v>
       </c>
-      <c r="N25" s="1">
+      <c r="N25">
         <f t="shared" si="2"/>
         <v>-3</v>
       </c>
@@ -2878,7 +2730,7 @@
         <f t="shared" si="7"/>
         <v>1100</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N26">
         <f t="shared" si="2"/>
         <v>-3.4000000000000004</v>
       </c>
@@ -2931,13 +2783,13 @@
         <f t="shared" si="8"/>
         <v>1200</v>
       </c>
-      <c r="N27" s="1">
+      <c r="N27">
         <f t="shared" si="2"/>
         <v>-4.8</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N28" s="1">
+      <c r="N28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2962,7 +2814,7 @@
       <c r="M29">
         <v>1300</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N29">
         <f t="shared" si="2"/>
         <v>-4</v>
       </c>
@@ -2987,7 +2839,7 @@
       <c r="M30">
         <v>200</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30">
         <f t="shared" si="2"/>
         <v>-0.4</v>
       </c>
@@ -3012,7 +2864,7 @@
       <c r="M31">
         <v>200</v>
       </c>
-      <c r="N31" s="1">
+      <c r="N31">
         <f t="shared" si="2"/>
         <v>-0.4</v>
       </c>
@@ -3037,7 +2889,7 @@
       <c r="M32">
         <v>300</v>
       </c>
-      <c r="N32" s="1">
+      <c r="N32">
         <f t="shared" si="2"/>
         <v>-0.6</v>
       </c>
@@ -3062,7 +2914,7 @@
       <c r="M33">
         <v>200</v>
       </c>
-      <c r="N33" s="1">
+      <c r="N33">
         <f t="shared" ref="N33:N36" si="9">C33-D33*20-E33*0.8-F33*0.6-H33*5+I33*10+J33/300</f>
         <v>-0.6</v>
       </c>
@@ -3087,7 +2939,7 @@
       <c r="M34">
         <v>200</v>
       </c>
-      <c r="N34" s="1">
+      <c r="N34">
         <f t="shared" si="9"/>
         <v>-1.8</v>
       </c>
@@ -3112,7 +2964,7 @@
       <c r="M35">
         <v>300</v>
       </c>
-      <c r="N35" s="1">
+      <c r="N35">
         <f t="shared" si="9"/>
         <v>-1.5</v>
       </c>
@@ -3137,7 +2989,7 @@
       <c r="M36">
         <v>400</v>
       </c>
-      <c r="N36" s="1">
+      <c r="N36">
         <f t="shared" si="9"/>
         <v>-1.5</v>
       </c>
@@ -3162,7 +3014,7 @@
       <c r="M37">
         <v>500</v>
       </c>
-      <c r="N37" s="1">
+      <c r="N37">
         <f t="shared" ref="N37:N62" si="10">C37-D37*20-E37*0.8-F37*0.6-H37*5+I37*10+J37/300</f>
         <v>-2.2000000000000002</v>
       </c>
@@ -3190,7 +3042,7 @@
       <c r="M38">
         <v>500</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N38">
         <f t="shared" si="10"/>
         <v>-1.8</v>
       </c>
@@ -3215,7 +3067,7 @@
       <c r="M39">
         <v>550</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N39">
         <f t="shared" si="10"/>
         <v>-2</v>
       </c>
@@ -3240,7 +3092,7 @@
       <c r="M40">
         <v>600</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N40">
         <f t="shared" si="10"/>
         <v>-2.2000000000000002</v>
       </c>
@@ -3265,7 +3117,7 @@
       <c r="M41">
         <v>200</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N41">
         <f>C41-D41*20-E41*0.8-F41*0.6-H41*5+I41*10+J41/300</f>
         <v>-1.6</v>
       </c>
@@ -3290,7 +3142,7 @@
       <c r="M42">
         <v>200</v>
       </c>
-      <c r="N42" s="1">
+      <c r="N42">
         <f>C42-D42*20-E42*0.8-F42*0.6-H42*5+I42*10+J42/300</f>
         <v>-0.9</v>
       </c>
@@ -3315,7 +3167,7 @@
       <c r="M43">
         <v>1000</v>
       </c>
-      <c r="N43" s="1">
+      <c r="N43">
         <f t="shared" si="10"/>
         <v>-3.1</v>
       </c>
@@ -3343,7 +3195,7 @@
       <c r="M44">
         <v>1100</v>
       </c>
-      <c r="N44" s="1">
+      <c r="N44">
         <f t="shared" si="10"/>
         <v>-3.1</v>
       </c>
@@ -3371,7 +3223,7 @@
       <c r="M45">
         <v>1200</v>
       </c>
-      <c r="N45" s="1">
+      <c r="N45">
         <f t="shared" si="10"/>
         <v>-2.7</v>
       </c>
@@ -3396,7 +3248,7 @@
       <c r="M46">
         <v>1300</v>
       </c>
-      <c r="N46" s="1">
+      <c r="N46">
         <f t="shared" si="10"/>
         <v>-2.7</v>
       </c>
@@ -3427,7 +3279,7 @@
       <c r="M47">
         <v>1000</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N47">
         <f t="shared" si="10"/>
         <v>-0.1</v>
       </c>
@@ -3448,7 +3300,7 @@
       <c r="M48">
         <v>1400</v>
       </c>
-      <c r="N48" s="1">
+      <c r="N48">
         <f t="shared" si="10"/>
         <v>-2.8</v>
       </c>
@@ -3479,7 +3331,7 @@
       <c r="M49">
         <v>700</v>
       </c>
-      <c r="N49" s="1">
+      <c r="N49">
         <f t="shared" si="10"/>
         <v>-2.7</v>
       </c>
@@ -3507,7 +3359,7 @@
       <c r="M50">
         <v>0</v>
       </c>
-      <c r="N50" s="1">
+      <c r="N50">
         <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
@@ -3532,7 +3384,7 @@
       <c r="M51">
         <v>0</v>
       </c>
-      <c r="N51" s="1">
+      <c r="N51">
         <f t="shared" si="10"/>
         <v>1.6</v>
       </c>
@@ -3557,7 +3409,7 @@
       <c r="M52">
         <v>0</v>
       </c>
-      <c r="N52" s="1">
+      <c r="N52">
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
@@ -3582,7 +3434,7 @@
       <c r="M53">
         <v>0</v>
       </c>
-      <c r="N53" s="1">
+      <c r="N53">
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
@@ -3639,7 +3491,7 @@
         <f t="shared" si="11"/>
         <v>1600</v>
       </c>
-      <c r="N54" s="1">
+      <c r="N54">
         <f t="shared" si="10"/>
         <v>-2.4</v>
       </c>
@@ -3745,13 +3597,13 @@
         <f t="shared" si="13"/>
         <v>2000</v>
       </c>
-      <c r="N56" s="1">
+      <c r="N56">
         <f t="shared" si="10"/>
         <v>-4.2</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N57" s="1">
+      <c r="N57">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -3776,7 +3628,7 @@
       <c r="M58">
         <v>500</v>
       </c>
-      <c r="N58" s="1">
+      <c r="N58">
         <f t="shared" si="10"/>
         <v>-0.6</v>
       </c>
@@ -3801,7 +3653,7 @@
       <c r="M59">
         <v>550</v>
       </c>
-      <c r="N59" s="1">
+      <c r="N59">
         <f t="shared" si="10"/>
         <v>-1.3</v>
       </c>
@@ -3826,7 +3678,7 @@
       <c r="M60">
         <v>600</v>
       </c>
-      <c r="N60" s="1">
+      <c r="N60">
         <f t="shared" si="10"/>
         <v>-2</v>
       </c>
@@ -3851,7 +3703,7 @@
       <c r="M61">
         <v>1200</v>
       </c>
-      <c r="N61" s="1">
+      <c r="N61">
         <f t="shared" si="10"/>
         <v>-3</v>
       </c>
@@ -3867,7 +3719,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N62" s="1">
+      <c r="N62">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -3892,7 +3744,7 @@
       <c r="M63">
         <v>1400</v>
       </c>
-      <c r="N63" s="1">
+      <c r="N63">
         <f t="shared" ref="N63:N77" si="14">C63-D63*20-E63*0.8-F63*0.6-H63*5+I63*10+J63/300</f>
         <v>-5.0999999999999996</v>
       </c>
@@ -3923,7 +3775,7 @@
       <c r="M64">
         <v>1300</v>
       </c>
-      <c r="N64" s="1">
+      <c r="N64">
         <f t="shared" si="14"/>
         <v>-4.9000000000000004</v>
       </c>
@@ -3954,7 +3806,7 @@
       <c r="M65">
         <v>1100</v>
       </c>
-      <c r="N65" s="1">
+      <c r="N65">
         <f t="shared" si="14"/>
         <v>-4.4000000000000004</v>
       </c>
@@ -3982,7 +3834,7 @@
       <c r="M66">
         <v>1800</v>
       </c>
-      <c r="N66" s="1">
+      <c r="N66">
         <f t="shared" si="14"/>
         <v>-4.8000000000000007</v>
       </c>
@@ -4013,7 +3865,7 @@
       <c r="M67">
         <v>1600</v>
       </c>
-      <c r="N67" s="1">
+      <c r="N67">
         <f t="shared" si="14"/>
         <v>-4.3000000000000007</v>
       </c>
@@ -4038,7 +3890,7 @@
       <c r="M68">
         <v>1700</v>
       </c>
-      <c r="N68" s="1">
+      <c r="N68">
         <f t="shared" si="14"/>
         <v>-4.3000000000000007</v>
       </c>
@@ -4063,7 +3915,7 @@
       <c r="M69">
         <v>2000</v>
       </c>
-      <c r="N69" s="1">
+      <c r="N69">
         <f t="shared" si="14"/>
         <v>-4.3000000000000007</v>
       </c>
@@ -4088,7 +3940,7 @@
       <c r="M70">
         <v>300</v>
       </c>
-      <c r="N70" s="1">
+      <c r="N70">
         <f>C70-D70*20-E70*0.8-F70*0.6-H70*5+I70*10+J70/300</f>
         <v>-0.6</v>
       </c>
@@ -4113,7 +3965,7 @@
       <c r="M71">
         <v>300</v>
       </c>
-      <c r="N71" s="1">
+      <c r="N71">
         <f t="shared" si="14"/>
         <v>-0.6</v>
       </c>
@@ -4138,7 +3990,7 @@
       <c r="M72">
         <v>1700</v>
       </c>
-      <c r="N72" s="1">
+      <c r="N72">
         <f t="shared" si="14"/>
         <v>-4.4000000000000004</v>
       </c>
@@ -4166,7 +4018,7 @@
       <c r="M73">
         <v>1500</v>
       </c>
-      <c r="N73" s="1">
+      <c r="N73">
         <f t="shared" si="14"/>
         <v>-3.9</v>
       </c>
@@ -4191,7 +4043,7 @@
       <c r="M74">
         <v>1600</v>
       </c>
-      <c r="N74" s="1">
+      <c r="N74">
         <f>C74-D74*20-E74*0.8-F74*0.6-H74*5+I74*10+J74/300</f>
         <v>-3.9</v>
       </c>
@@ -4216,7 +4068,7 @@
       <c r="M75">
         <v>0</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N75">
         <f>C75-D75*20-E75*0.8-F75*0.6-H75*5+I75*10+J75/300</f>
         <v>0</v>
       </c>
@@ -4241,7 +4093,7 @@
       <c r="M76">
         <v>0</v>
       </c>
-      <c r="N76" s="1">
+      <c r="N76">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -4266,7 +4118,7 @@
       <c r="M77">
         <v>0</v>
       </c>
-      <c r="N77" s="1">
+      <c r="N77">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -4291,7 +4143,7 @@
       <c r="M78">
         <v>0</v>
       </c>
-      <c r="N78" s="1">
+      <c r="N78">
         <f>C78-D78*20-E78*0.8-F78*0.6-H78*5+I78*10+J78/300</f>
         <v>0</v>
       </c>
@@ -4301,7 +4153,7 @@
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N79" s="1">
+      <c r="N79">
         <f t="shared" ref="N79:N119" si="15">C79-D79*20-E79*0.8-F79*0.6-H79*5+I79*10+J79/300</f>
         <v>0</v>
       </c>
@@ -4326,7 +4178,7 @@
       <c r="M80">
         <v>200</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N80">
         <f t="shared" ref="N80:N88" si="16">C80-D80*20-E80*0.8-F80*0.6-H80*5+I80*10+J80/300</f>
         <v>-1.7</v>
       </c>
@@ -4351,7 +4203,7 @@
       <c r="M81">
         <v>900</v>
       </c>
-      <c r="N81" s="1">
+      <c r="N81">
         <f t="shared" si="16"/>
         <v>-2.6</v>
       </c>
@@ -4379,7 +4231,7 @@
       <c r="M82">
         <v>900</v>
       </c>
-      <c r="N82" s="1">
+      <c r="N82">
         <f t="shared" si="16"/>
         <v>-2.6</v>
       </c>
@@ -4389,7 +4241,7 @@
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N83" s="1">
+      <c r="N83">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -4414,7 +4266,7 @@
       <c r="M84">
         <v>200</v>
       </c>
-      <c r="N84" s="1">
+      <c r="N84">
         <f t="shared" si="16"/>
         <v>-0.6</v>
       </c>
@@ -4439,7 +4291,7 @@
       <c r="M85">
         <v>300</v>
       </c>
-      <c r="N85" s="1">
+      <c r="N85">
         <f t="shared" si="16"/>
         <v>-1.9000000000000001</v>
       </c>
@@ -4464,7 +4316,7 @@
       <c r="M86">
         <v>400</v>
       </c>
-      <c r="N86" s="1">
+      <c r="N86">
         <f t="shared" si="16"/>
         <v>-2.8</v>
       </c>
@@ -4492,7 +4344,7 @@
       <c r="M87">
         <v>600</v>
       </c>
-      <c r="N87" s="1">
+      <c r="N87">
         <f t="shared" si="16"/>
         <v>-2.2000000000000002</v>
       </c>
@@ -4517,7 +4369,7 @@
       <c r="M88">
         <v>800</v>
       </c>
-      <c r="N88" s="1">
+      <c r="N88">
         <f t="shared" si="16"/>
         <v>-3.2</v>
       </c>
@@ -4527,7 +4379,7 @@
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N89" s="1">
+      <c r="N89">
         <f>C89-D89*20-E89*0.8-F89*0.6-H89*5+I89*10+J89/300</f>
         <v>0</v>
       </c>
@@ -4552,7 +4404,7 @@
       <c r="M90">
         <v>300</v>
       </c>
-      <c r="N90" s="1">
+      <c r="N90">
         <f>C90-D90*20-E90*0.8-F90*0.6-H90*5+I90*10+J90/300</f>
         <v>-0.6</v>
       </c>
@@ -4580,7 +4432,7 @@
       <c r="M91">
         <v>200</v>
       </c>
-      <c r="N91" s="1">
+      <c r="N91">
         <f>C91-D91*20-E91*0.8-F91*0.6-H91*5+I91*10+J91/300</f>
         <v>-1.4</v>
       </c>
@@ -4605,7 +4457,7 @@
       <c r="M92">
         <v>1000</v>
       </c>
-      <c r="N92" s="1">
+      <c r="N92">
         <f>C92-D92*20-E92*0.8-F92*0.6-H92*5+I92*10+J92/300</f>
         <v>-3.8000000000000003</v>
       </c>
@@ -4618,7 +4470,7 @@
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N93" s="1">
+      <c r="N93">
         <f t="shared" ref="N93:N104" si="18">C93-D93*20-E93*0.8-F93*0.6-H93*5+I93*10+J93/300</f>
         <v>0</v>
       </c>
@@ -4643,7 +4495,7 @@
       <c r="M94">
         <v>400</v>
       </c>
-      <c r="N94" s="1">
+      <c r="N94">
         <f t="shared" si="18"/>
         <v>-0.6</v>
       </c>
@@ -4668,7 +4520,7 @@
       <c r="M95">
         <v>700</v>
       </c>
-      <c r="N95" s="1">
+      <c r="N95">
         <f t="shared" si="18"/>
         <v>-4.2</v>
       </c>
@@ -4696,13 +4548,13 @@
       <c r="M96">
         <v>50</v>
       </c>
-      <c r="N96" s="1">
+      <c r="N96">
         <f t="shared" si="18"/>
         <v>0.6</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N97" s="1">
+      <c r="N97">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -4727,7 +4579,7 @@
       <c r="M98">
         <v>300</v>
       </c>
-      <c r="N98" s="1">
+      <c r="N98">
         <f t="shared" si="18"/>
         <v>-1</v>
       </c>
@@ -4752,7 +4604,7 @@
       <c r="M99">
         <v>1000</v>
       </c>
-      <c r="N99" s="1">
+      <c r="N99">
         <f t="shared" si="18"/>
         <v>-5.4</v>
       </c>
@@ -4765,7 +4617,7 @@
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N100" s="1">
+      <c r="N100">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -4790,7 +4642,7 @@
       <c r="M101">
         <v>900</v>
       </c>
-      <c r="N101" s="1">
+      <c r="N101">
         <f t="shared" si="18"/>
         <v>-3.2</v>
       </c>
@@ -4818,7 +4670,7 @@
       <c r="M102">
         <v>1000</v>
       </c>
-      <c r="N102" s="1">
+      <c r="N102">
         <f t="shared" si="18"/>
         <v>-3.9</v>
       </c>
@@ -4846,7 +4698,7 @@
       <c r="M103">
         <v>1000</v>
       </c>
-      <c r="N103" s="1">
+      <c r="N103">
         <f t="shared" si="18"/>
         <v>-3.8</v>
       </c>
@@ -4877,7 +4729,7 @@
       <c r="M104">
         <v>600</v>
       </c>
-      <c r="N104" s="1">
+      <c r="N104">
         <f t="shared" si="18"/>
         <v>-8.65</v>
       </c>
@@ -4911,7 +4763,7 @@
       <c r="M105">
         <v>2000</v>
       </c>
-      <c r="N105" s="1">
+      <c r="N105">
         <f t="shared" si="15"/>
         <v>-11.450000000000001</v>
       </c>
@@ -4939,7 +4791,7 @@
       <c r="M106">
         <v>1000</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N106">
         <f t="shared" si="15"/>
         <v>-5.2</v>
       </c>
@@ -4967,7 +4819,7 @@
       <c r="M107">
         <v>1200</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N107">
         <f t="shared" si="15"/>
         <v>-4.2</v>
       </c>
@@ -4995,7 +4847,7 @@
       <c r="M108">
         <v>1000</v>
       </c>
-      <c r="N108" s="1">
+      <c r="N108">
         <f t="shared" si="15"/>
         <v>-4.2</v>
       </c>
@@ -5023,7 +4875,7 @@
       <c r="M109">
         <v>800</v>
       </c>
-      <c r="N109" s="1">
+      <c r="N109">
         <f t="shared" si="15"/>
         <v>-6</v>
       </c>
@@ -5051,7 +4903,7 @@
       <c r="M110">
         <v>500</v>
       </c>
-      <c r="N110" s="1">
+      <c r="N110">
         <f t="shared" si="15"/>
         <v>-3.4000000000000004</v>
       </c>
@@ -5076,7 +4928,7 @@
       <c r="M111">
         <v>1600</v>
       </c>
-      <c r="N111" s="1">
+      <c r="N111">
         <f t="shared" si="15"/>
         <v>-4.9000000000000004</v>
       </c>
@@ -5104,7 +4956,7 @@
       <c r="M112">
         <v>1500</v>
       </c>
-      <c r="N112" s="1">
+      <c r="N112">
         <f t="shared" si="15"/>
         <v>-3.6</v>
       </c>
@@ -5132,7 +4984,7 @@
       <c r="M113">
         <v>1700</v>
       </c>
-      <c r="N113" s="1">
+      <c r="N113">
         <f t="shared" si="15"/>
         <v>-3.6</v>
       </c>
@@ -5142,7 +4994,7 @@
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N114" s="1">
+      <c r="N114">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
@@ -5152,30 +5004,22 @@
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>32</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" t="s">
         <v>33</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C115">
         <v>-0.5</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D115">
         <v>0.04</v>
       </c>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-      <c r="K115" s="1"/>
-      <c r="L115" s="1"/>
-      <c r="M115" s="1">
+      <c r="M115">
         <v>400</v>
       </c>
-      <c r="N115" s="1">
+      <c r="N115">
         <f t="shared" si="15"/>
         <v>-1.3</v>
       </c>
@@ -5185,30 +5029,22 @@
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
+      <c r="A116" t="s">
         <v>34</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" t="s">
         <v>35</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C116">
         <v>-0.5</v>
       </c>
-      <c r="D116" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
-      <c r="K116" s="1"/>
-      <c r="L116" s="1"/>
-      <c r="M116" s="1">
+      <c r="D116">
+        <v>0.02</v>
+      </c>
+      <c r="M116">
         <v>200</v>
       </c>
-      <c r="N116" s="1">
+      <c r="N116">
         <f t="shared" si="15"/>
         <v>-0.9</v>
       </c>
@@ -5233,7 +5069,7 @@
       <c r="M117">
         <v>350</v>
       </c>
-      <c r="N117" s="1">
+      <c r="N117">
         <f t="shared" si="15"/>
         <v>-0.6</v>
       </c>
@@ -5258,7 +5094,7 @@
       <c r="M118">
         <v>200</v>
       </c>
-      <c r="N118" s="1">
+      <c r="N118">
         <f t="shared" si="15"/>
         <v>-0.6</v>
       </c>
@@ -5283,7 +5119,7 @@
       <c r="M119">
         <v>100</v>
       </c>
-      <c r="N119" s="1">
+      <c r="N119">
         <f t="shared" si="15"/>
         <v>-1.5</v>
       </c>
@@ -5308,7 +5144,7 @@
       <c r="M120">
         <v>1200</v>
       </c>
-      <c r="N120" s="1">
+      <c r="N120">
         <f t="shared" ref="N120:N125" si="19">C120-D120*20-E120*0.8-F120*0.6-H120*5+I120*10+J120/300</f>
         <v>-5</v>
       </c>
@@ -5336,7 +5172,7 @@
       <c r="M121">
         <v>1200</v>
       </c>
-      <c r="N121" s="1">
+      <c r="N121">
         <f t="shared" si="19"/>
         <v>-5</v>
       </c>
@@ -5361,7 +5197,7 @@
       <c r="M122">
         <v>1500</v>
       </c>
-      <c r="N122" s="1">
+      <c r="N122">
         <f t="shared" si="19"/>
         <v>-5</v>
       </c>
@@ -5386,7 +5222,7 @@
       <c r="M123">
         <v>1500</v>
       </c>
-      <c r="N123" s="1">
+      <c r="N123">
         <f t="shared" si="19"/>
         <v>-5</v>
       </c>
@@ -5411,7 +5247,7 @@
       <c r="M124">
         <v>1300</v>
       </c>
-      <c r="N124" s="1">
+      <c r="N124">
         <f t="shared" si="19"/>
         <v>-2.6</v>
       </c>
@@ -5424,20 +5260,7 @@
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="1"/>
-      <c r="N125" s="1">
+      <c r="N125">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
@@ -5462,7 +5285,7 @@
       <c r="M126">
         <v>300</v>
       </c>
-      <c r="N126" s="1">
+      <c r="N126">
         <f>C126-D126*20-E126*0.8-F126*0.6-H126*5+I126*10+J126/300</f>
         <v>-1.2</v>
       </c>
@@ -5490,7 +5313,7 @@
       <c r="M127">
         <v>1200</v>
       </c>
-      <c r="N127" s="1">
+      <c r="N127">
         <f>C127-D127*20-E127*0.8-F127*0.6-H127*5+I127*10+J127/300</f>
         <v>-6.2</v>
       </c>
@@ -5503,7 +5326,7 @@
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N128" s="1">
+      <c r="N128">
         <f>C128-D128*20-E128*0.8-F128*0.6-H128*5+I128*10+J128/300</f>
         <v>0</v>
       </c>
@@ -5528,7 +5351,7 @@
       <c r="M129">
         <v>300</v>
       </c>
-      <c r="N129" s="1">
+      <c r="N129">
         <f>C129-D129*20-E129*0.8-F129*0.6-H129*5+I129*10+J129/300</f>
         <v>-1.2</v>
       </c>
@@ -5556,7 +5379,7 @@
       <c r="M130">
         <v>950</v>
       </c>
-      <c r="N130" s="1">
+      <c r="N130">
         <f>C130-D130*20-E130*0.8-F130*0.6-H130*5+I130*10+J130/300</f>
         <v>-6.8</v>
       </c>
@@ -5569,7 +5392,7 @@
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="N131" s="1">
+      <c r="N131">
         <f t="shared" ref="N131:N168" si="20">C131-D131*20-E131*0.8-F131*0.6-H131*5+I131*10+J131/300</f>
         <v>0</v>
       </c>
@@ -5594,7 +5417,7 @@
       <c r="M132">
         <v>400</v>
       </c>
-      <c r="N132" s="1">
+      <c r="N132">
         <f t="shared" si="20"/>
         <v>-1.2</v>
       </c>
@@ -5619,7 +5442,7 @@
       <c r="M133">
         <v>750</v>
       </c>
-      <c r="N133" s="1">
+      <c r="N133">
         <f t="shared" si="20"/>
         <v>-6.2</v>
       </c>
@@ -5632,7 +5455,7 @@
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="N134" s="1">
+      <c r="N134">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
@@ -5657,7 +5480,7 @@
       <c r="M135">
         <v>400</v>
       </c>
-      <c r="N135" s="1">
+      <c r="N135">
         <f t="shared" si="20"/>
         <v>-1.2</v>
       </c>
@@ -5682,7 +5505,7 @@
       <c r="M136">
         <v>750</v>
       </c>
-      <c r="N136" s="1">
+      <c r="N136">
         <f t="shared" si="20"/>
         <v>-6.3000000000000007</v>
       </c>
@@ -5710,7 +5533,7 @@
       <c r="M137">
         <v>800</v>
       </c>
-      <c r="N137" s="1">
+      <c r="N137">
         <f t="shared" si="20"/>
         <v>-6.2</v>
       </c>
@@ -5720,7 +5543,7 @@
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="N138" s="1">
+      <c r="N138">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
@@ -5745,7 +5568,7 @@
       <c r="M139">
         <v>400</v>
       </c>
-      <c r="N139" s="1">
+      <c r="N139">
         <f t="shared" si="20"/>
         <v>-1.2</v>
       </c>
@@ -5776,7 +5599,7 @@
       <c r="M140">
         <v>400</v>
       </c>
-      <c r="N140" s="1">
+      <c r="N140">
         <f t="shared" si="20"/>
         <v>-1.2</v>
       </c>
@@ -5804,7 +5627,7 @@
       <c r="M141">
         <v>1000</v>
       </c>
-      <c r="N141" s="1">
+      <c r="N141">
         <f t="shared" si="20"/>
         <v>-6</v>
       </c>
@@ -5835,7 +5658,7 @@
       <c r="M142">
         <v>1000</v>
       </c>
-      <c r="N142" s="1">
+      <c r="N142">
         <f t="shared" si="20"/>
         <v>-6</v>
       </c>
@@ -5863,7 +5686,7 @@
       <c r="M143">
         <v>1900</v>
       </c>
-      <c r="N143" s="1">
+      <c r="N143">
         <f t="shared" si="20"/>
         <v>-5.8</v>
       </c>
@@ -5894,7 +5717,7 @@
       <c r="M144">
         <v>1900</v>
       </c>
-      <c r="N144" s="1">
+      <c r="N144">
         <f t="shared" si="20"/>
         <v>-5.8</v>
       </c>
@@ -5922,7 +5745,7 @@
       <c r="M145">
         <v>1500</v>
       </c>
-      <c r="N145" s="1">
+      <c r="N145">
         <f t="shared" si="20"/>
         <v>-5.6000000000000005</v>
       </c>
@@ -5953,7 +5776,7 @@
       <c r="M146">
         <v>1500</v>
       </c>
-      <c r="N146" s="1">
+      <c r="N146">
         <f t="shared" si="20"/>
         <v>-5.6000000000000005</v>
       </c>
@@ -5981,7 +5804,7 @@
       <c r="M147">
         <v>1800</v>
       </c>
-      <c r="N147" s="1">
+      <c r="N147">
         <f t="shared" si="20"/>
         <v>-5.6000000000000005</v>
       </c>
@@ -6012,7 +5835,7 @@
       <c r="M148">
         <v>1800</v>
       </c>
-      <c r="N148" s="1">
+      <c r="N148">
         <f t="shared" si="20"/>
         <v>-5.6000000000000005</v>
       </c>
@@ -6040,7 +5863,7 @@
       <c r="M149">
         <v>1600</v>
       </c>
-      <c r="N149" s="1">
+      <c r="N149">
         <f t="shared" si="20"/>
         <v>-5.6000000000000005</v>
       </c>
@@ -6068,7 +5891,7 @@
       <c r="M150">
         <v>1600</v>
       </c>
-      <c r="N150" s="1">
+      <c r="N150">
         <f t="shared" si="20"/>
         <v>-5.6000000000000005</v>
       </c>
@@ -6078,7 +5901,7 @@
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N151" s="1">
+      <c r="N151">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
@@ -6100,7 +5923,7 @@
       <c r="M152">
         <v>100</v>
       </c>
-      <c r="N152" s="1">
+      <c r="N152">
         <f t="shared" si="20"/>
         <v>-0.8</v>
       </c>
@@ -6128,7 +5951,7 @@
       <c r="M153">
         <v>1000</v>
       </c>
-      <c r="N153" s="1">
+      <c r="N153">
         <f t="shared" si="20"/>
         <v>-6.4</v>
       </c>
@@ -6159,7 +5982,7 @@
       <c r="M154">
         <v>1200</v>
       </c>
-      <c r="N154" s="1">
+      <c r="N154">
         <f t="shared" si="20"/>
         <v>-6.4</v>
       </c>
@@ -6169,7 +5992,7 @@
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N155" s="1">
+      <c r="N155">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
@@ -6194,7 +6017,7 @@
       <c r="M156">
         <v>1000</v>
       </c>
-      <c r="N156" s="1">
+      <c r="N156">
         <f t="shared" si="20"/>
         <v>-1.7</v>
       </c>
@@ -6222,7 +6045,7 @@
       <c r="M157">
         <v>0</v>
       </c>
-      <c r="N157" s="1">
+      <c r="N157">
         <f t="shared" si="20"/>
         <v>-0.2</v>
       </c>
@@ -6247,7 +6070,7 @@
       <c r="M158">
         <v>200</v>
       </c>
-      <c r="N158" s="1">
+      <c r="N158">
         <f t="shared" si="20"/>
         <v>-0.6</v>
       </c>
@@ -6272,7 +6095,7 @@
       <c r="M159">
         <v>200</v>
       </c>
-      <c r="N159" s="1">
+      <c r="N159">
         <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
@@ -6297,7 +6120,7 @@
       <c r="M160">
         <v>200</v>
       </c>
-      <c r="N160" s="1">
+      <c r="N160">
         <f t="shared" si="20"/>
         <v>-0.6</v>
       </c>
@@ -6322,7 +6145,7 @@
       <c r="M161">
         <v>200</v>
       </c>
-      <c r="N161" s="1">
+      <c r="N161">
         <f t="shared" si="20"/>
         <v>-0.2</v>
       </c>
@@ -6347,7 +6170,7 @@
       <c r="M162">
         <v>300</v>
       </c>
-      <c r="N162" s="1">
+      <c r="N162">
         <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
@@ -6372,7 +6195,7 @@
       <c r="M163">
         <v>300</v>
       </c>
-      <c r="N163" s="1">
+      <c r="N163">
         <f t="shared" si="20"/>
         <v>-0.4</v>
       </c>
@@ -6397,7 +6220,7 @@
       <c r="M164">
         <v>800</v>
       </c>
-      <c r="N164" s="1">
+      <c r="N164">
         <f t="shared" si="20"/>
         <v>-3.2</v>
       </c>
@@ -6425,7 +6248,7 @@
       <c r="M165">
         <v>750</v>
       </c>
-      <c r="N165" s="1">
+      <c r="N165">
         <f t="shared" si="20"/>
         <v>-3.5</v>
       </c>
@@ -6453,7 +6276,7 @@
       <c r="M166">
         <v>500</v>
       </c>
-      <c r="N166" s="1">
+      <c r="N166">
         <f t="shared" si="20"/>
         <v>-2.8</v>
       </c>
@@ -6481,7 +6304,7 @@
       <c r="M167">
         <v>500</v>
       </c>
-      <c r="N167" s="1">
+      <c r="N167">
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
@@ -6498,7 +6321,7 @@
         <v>217</v>
       </c>
       <c r="C168">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D168">
         <v>0.27</v>
@@ -6509,9 +6332,9 @@
       <c r="M168">
         <v>4000</v>
       </c>
-      <c r="N168" s="1">
+      <c r="N168">
         <f t="shared" si="20"/>
-        <v>-9.2000000000000011</v>
+        <v>-10.200000000000001</v>
       </c>
       <c r="P168">
         <v>20.100000000000001</v>
@@ -6522,7 +6345,7 @@
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N169" s="1">
+      <c r="N169">
         <f t="shared" ref="N169:N209" si="22">C169-D169*20-E169*0.8-F169*0.6-H169*5+I169*10+J169/300</f>
         <v>0</v>
       </c>
@@ -6547,7 +6370,7 @@
       <c r="M170">
         <v>1000</v>
       </c>
-      <c r="N170" s="1">
+      <c r="N170">
         <f t="shared" si="22"/>
         <v>-1.9000000000000001</v>
       </c>
@@ -6575,7 +6398,7 @@
       <c r="M171">
         <v>0</v>
       </c>
-      <c r="N171" s="1">
+      <c r="N171">
         <f t="shared" si="22"/>
         <v>-0.2</v>
       </c>
@@ -6600,7 +6423,7 @@
       <c r="M172">
         <v>200</v>
       </c>
-      <c r="N172" s="1">
+      <c r="N172">
         <f t="shared" si="22"/>
         <v>-0.6</v>
       </c>
@@ -6625,7 +6448,7 @@
       <c r="M173">
         <v>200</v>
       </c>
-      <c r="N173" s="1">
+      <c r="N173">
         <f t="shared" si="22"/>
         <v>-0.6</v>
       </c>
@@ -6650,7 +6473,7 @@
       <c r="M174">
         <v>500</v>
       </c>
-      <c r="N174" s="1">
+      <c r="N174">
         <f t="shared" si="22"/>
         <v>-3.2</v>
       </c>
@@ -6681,7 +6504,7 @@
       <c r="M175">
         <v>5000</v>
       </c>
-      <c r="N175" s="1">
+      <c r="N175">
         <f t="shared" si="22"/>
         <v>-13</v>
       </c>
@@ -6694,7 +6517,6 @@
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N176" s="1"/>
       <c r="Q176">
         <f t="shared" si="21"/>
         <v>0.02</v>
@@ -6716,7 +6538,7 @@
       <c r="M177">
         <v>400</v>
       </c>
-      <c r="N177" s="1">
+      <c r="N177">
         <f t="shared" si="22"/>
         <v>-1</v>
       </c>
@@ -6726,30 +6548,22 @@
       </c>
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
+      <c r="A178" t="s">
         <v>270</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B178" t="s">
         <v>166</v>
       </c>
-      <c r="C178" s="1">
+      <c r="C178">
         <v>-2</v>
       </c>
-      <c r="D178" s="1">
+      <c r="D178">
         <v>0.16</v>
       </c>
-      <c r="E178" s="1"/>
-      <c r="F178" s="1"/>
-      <c r="G178" s="1"/>
-      <c r="H178" s="1"/>
-      <c r="I178" s="1"/>
-      <c r="J178" s="1"/>
-      <c r="K178" s="1"/>
-      <c r="L178" s="1"/>
-      <c r="M178" s="1">
+      <c r="M178">
         <v>1000</v>
       </c>
-      <c r="N178" s="1">
+      <c r="N178">
         <f t="shared" si="22"/>
         <v>-5.2</v>
       </c>
@@ -6762,20 +6576,6 @@
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A179" s="1"/>
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
-      <c r="E179" s="1"/>
-      <c r="F179" s="1"/>
-      <c r="G179" s="1"/>
-      <c r="H179" s="1"/>
-      <c r="I179" s="1"/>
-      <c r="J179" s="1"/>
-      <c r="K179" s="1"/>
-      <c r="L179" s="1"/>
-      <c r="M179" s="1"/>
-      <c r="N179" s="1"/>
       <c r="Q179">
         <f t="shared" si="21"/>
         <v>0.02</v>
@@ -6800,7 +6600,7 @@
       <c r="M180">
         <v>1000</v>
       </c>
-      <c r="N180" s="1">
+      <c r="N180">
         <f t="shared" si="22"/>
         <v>-6.8000000000000007</v>
       </c>
@@ -6831,7 +6631,7 @@
       <c r="M181">
         <v>2000</v>
       </c>
-      <c r="N181" s="1">
+      <c r="N181">
         <f t="shared" si="22"/>
         <v>-9</v>
       </c>
@@ -6862,7 +6662,7 @@
       <c r="M182">
         <v>3000</v>
       </c>
-      <c r="N182" s="1">
+      <c r="N182">
         <f t="shared" si="22"/>
         <v>-7.3000000000000016</v>
       </c>
@@ -6893,7 +6693,7 @@
       <c r="M183">
         <v>3000</v>
       </c>
-      <c r="N183" s="1">
+      <c r="N183">
         <f t="shared" si="22"/>
         <v>-6.6</v>
       </c>
@@ -6924,7 +6724,7 @@
       <c r="M184">
         <v>4000</v>
       </c>
-      <c r="N184" s="1">
+      <c r="N184">
         <f t="shared" si="22"/>
         <v>-7.9000000000000012</v>
       </c>
@@ -6955,7 +6755,7 @@
       <c r="M185">
         <v>2000</v>
       </c>
-      <c r="N185" s="1">
+      <c r="N185">
         <f t="shared" si="22"/>
         <v>-6.7</v>
       </c>
@@ -6968,7 +6768,7 @@
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N186" s="1">
+      <c r="N186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
@@ -6993,7 +6793,7 @@
       <c r="M187">
         <v>300</v>
       </c>
-      <c r="N187" s="1">
+      <c r="N187">
         <f t="shared" si="22"/>
         <v>-2</v>
       </c>
@@ -7018,7 +6818,7 @@
       <c r="M188">
         <v>300</v>
       </c>
-      <c r="N188" s="1">
+      <c r="N188">
         <f t="shared" si="22"/>
         <v>-2</v>
       </c>
@@ -7043,7 +6843,7 @@
       <c r="M189">
         <v>750</v>
       </c>
-      <c r="N189" s="1">
+      <c r="N189">
         <f t="shared" si="22"/>
         <v>-6.4</v>
       </c>
@@ -7071,7 +6871,7 @@
       <c r="M190">
         <v>1000</v>
       </c>
-      <c r="N190" s="1">
+      <c r="N190">
         <f t="shared" si="22"/>
         <v>-6.6</v>
       </c>
@@ -7084,7 +6884,7 @@
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N191" s="1">
+      <c r="N191">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
@@ -7112,7 +6912,7 @@
       <c r="M192">
         <v>3000</v>
       </c>
-      <c r="N192" s="1">
+      <c r="N192">
         <f t="shared" si="22"/>
         <v>-13.399999999999999</v>
       </c>
@@ -7122,7 +6922,7 @@
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N193" s="1">
+      <c r="N193">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
@@ -7147,7 +6947,7 @@
       <c r="M194">
         <v>1000</v>
       </c>
-      <c r="N194" s="1">
+      <c r="N194">
         <f t="shared" si="22"/>
         <v>-1.6</v>
       </c>
@@ -7175,7 +6975,7 @@
       <c r="M195">
         <v>700</v>
       </c>
-      <c r="N195" s="1">
+      <c r="N195">
         <f t="shared" si="22"/>
         <v>-4.2</v>
       </c>
@@ -7185,7 +6985,7 @@
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N196" s="1">
+      <c r="N196">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
@@ -7213,7 +7013,7 @@
       <c r="M197">
         <v>1200</v>
       </c>
-      <c r="N197" s="1">
+      <c r="N197">
         <f t="shared" si="22"/>
         <v>-6.6000000000000005</v>
       </c>
@@ -7238,7 +7038,7 @@
       <c r="M198">
         <v>0</v>
       </c>
-      <c r="N198" s="1">
+      <c r="N198">
         <f t="shared" si="22"/>
         <v>1.6</v>
       </c>
@@ -7263,7 +7063,7 @@
       <c r="M199">
         <v>0</v>
       </c>
-      <c r="N199" s="1">
+      <c r="N199">
         <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
@@ -7273,7 +7073,7 @@
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N200" s="1">
+      <c r="N200">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
@@ -7298,7 +7098,7 @@
       <c r="M201">
         <v>200</v>
       </c>
-      <c r="N201" s="1">
+      <c r="N201">
         <f t="shared" si="22"/>
         <v>-0.8</v>
       </c>
@@ -7323,7 +7123,7 @@
       <c r="M202">
         <v>300</v>
       </c>
-      <c r="N202" s="1">
+      <c r="N202">
         <f t="shared" si="22"/>
         <v>-0.4</v>
       </c>
@@ -7348,7 +7148,7 @@
       <c r="M203">
         <v>50</v>
       </c>
-      <c r="N203" s="1">
+      <c r="N203">
         <f t="shared" si="22"/>
         <v>-0.7</v>
       </c>
@@ -7373,7 +7173,7 @@
       <c r="M204">
         <v>50</v>
       </c>
-      <c r="N204" s="1">
+      <c r="N204">
         <f t="shared" si="22"/>
         <v>-0.7</v>
       </c>
@@ -7398,7 +7198,7 @@
       <c r="M205">
         <v>2000</v>
       </c>
-      <c r="N205" s="1">
+      <c r="N205">
         <f t="shared" si="22"/>
         <v>-2.8</v>
       </c>
@@ -7411,7 +7211,7 @@
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="N206" s="1">
+      <c r="N206">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
@@ -7436,7 +7236,7 @@
       <c r="M207">
         <v>100</v>
       </c>
-      <c r="N207" s="1">
+      <c r="N207">
         <f t="shared" si="22"/>
         <v>-0.6</v>
       </c>
@@ -7461,7 +7261,7 @@
       <c r="M208">
         <v>100</v>
       </c>
-      <c r="N208" s="1">
+      <c r="N208">
         <f t="shared" si="22"/>
         <v>-0.4</v>
       </c>
@@ -7486,7 +7286,7 @@
       <c r="M209">
         <v>700</v>
       </c>
-      <c r="N209" s="1">
+      <c r="N209">
         <f t="shared" si="22"/>
         <v>-3</v>
       </c>
